--- a/salidas/empresas/MO.xlsx
+++ b/salidas/empresas/MO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>4.802680969238281</v>
+        <v>4.802681446075439</v>
       </c>
       <c r="C2" t="n">
         <v>72.33999633789062</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>4.773471355438232</v>
+        <v>4.773470878601074</v>
       </c>
       <c r="C3" t="n">
         <v>71.90000152587891</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>4.755935668945312</v>
+        <v>4.755938529968262</v>
       </c>
       <c r="C4" t="n">
         <v>70.86000061035156</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>4.910306453704834</v>
+        <v>4.910307884216309</v>
       </c>
       <c r="C5" t="n">
         <v>73.16000366210938</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>4.855943202972412</v>
+        <v>4.855941772460938</v>
       </c>
       <c r="C6" t="n">
         <v>72.34999847412109</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>4.98452091217041</v>
+        <v>4.984522819519043</v>
       </c>
       <c r="C7" t="n">
         <v>73.43000030517578</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>5.428463459014893</v>
+        <v>5.428467273712158</v>
       </c>
       <c r="C8" t="n">
         <v>79.97000122070312</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>5.670120239257812</v>
+        <v>5.670121192932129</v>
       </c>
       <c r="C9" t="n">
         <v>83.52999877929688</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>5.250677108764648</v>
+        <v>5.250678062438965</v>
       </c>
       <c r="C10" t="n">
         <v>76.55000305175781</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>5.578543663024902</v>
+        <v>5.57854175567627</v>
       </c>
       <c r="C11" t="n">
         <v>81.33000183105469</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>5.776087284088135</v>
+        <v>5.776089668273926</v>
       </c>
       <c r="C12" t="n">
         <v>84.20999908447266</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>5.946174144744873</v>
+        <v>5.946176052093506</v>
       </c>
       <c r="C13" t="n">
         <v>85.81999969482422</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>6.054957389831543</v>
+        <v>6.054953575134277</v>
       </c>
       <c r="C14" t="n">
         <v>87.38999938964844</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>5.839472770690918</v>
+        <v>5.839474678039551</v>
       </c>
       <c r="C15" t="n">
         <v>84.27999877929688</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>6.145042419433594</v>
+        <v>6.145037174224854</v>
       </c>
       <c r="C16" t="n">
         <v>87.80999755859375</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>6.426547050476074</v>
+        <v>6.426549434661865</v>
       </c>
       <c r="C17" t="n">
         <v>68.91999816894531</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>6.605286598205566</v>
+        <v>6.605288982391357</v>
       </c>
       <c r="C19" t="n">
         <v>70.13999938964844</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>6.259674072265625</v>
+        <v>6.259672164916992</v>
       </c>
       <c r="C20" t="n">
         <v>66.47000122070312</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>6.536540985107422</v>
+        <v>6.536543846130371</v>
       </c>
       <c r="C21" t="n">
         <v>69.41000366210938</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>6.621150970458984</v>
+        <v>6.621150016784668</v>
       </c>
       <c r="C22" t="n">
         <v>69.52999877929688</v>
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>7.38582706451416</v>
+        <v>7.385823249816895</v>
       </c>
       <c r="C24" t="n">
         <v>77.55999755859375</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>7.267498970031738</v>
+        <v>7.267497539520264</v>
       </c>
       <c r="C25" t="n">
         <v>75.58000183105469</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>7.032873630523682</v>
+        <v>7.032878398895264</v>
       </c>
       <c r="C27" t="n">
         <v>73.13999938964844</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>6.994593143463135</v>
+        <v>6.994595050811768</v>
       </c>
       <c r="C28" t="n">
         <v>22.20000076293945</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>6.301434993743896</v>
+        <v>6.301435947418213</v>
       </c>
       <c r="C29" t="n">
         <v>20</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>7.01349925994873</v>
+        <v>7.013497352600098</v>
       </c>
       <c r="C30" t="n">
         <v>22.26000022888184</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>6.568018913269043</v>
+        <v>6.568016529083252</v>
       </c>
       <c r="C31" t="n">
         <v>20.55999946594238</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>6.500935077667236</v>
+        <v>6.500932693481445</v>
       </c>
       <c r="C32" t="n">
         <v>20.35000038146973</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>6.718163967132568</v>
+        <v>6.718163013458252</v>
       </c>
       <c r="C33" t="n">
         <v>21.03000068664551</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>6.437233448028564</v>
+        <v>6.437233924865723</v>
       </c>
       <c r="C34" t="n">
         <v>19.84000015258789</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>6.226337432861328</v>
+        <v>6.226339817047119</v>
       </c>
       <c r="C35" t="n">
         <v>19.19000053405762</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>5.21727466583252</v>
+        <v>5.217275142669678</v>
       </c>
       <c r="C36" t="n">
         <v>16.07999992370605</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>4.990850448608398</v>
+        <v>4.990850925445557</v>
       </c>
       <c r="C37" t="n">
         <v>15.0600004196167</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>5.481318473815918</v>
+        <v>5.481316089630127</v>
       </c>
       <c r="C38" t="n">
         <v>16.54000091552734</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>5.116779804229736</v>
+        <v>5.116780757904053</v>
       </c>
       <c r="C39" t="n">
         <v>15.4399995803833</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>5.414708614349365</v>
+        <v>5.414707183837891</v>
       </c>
       <c r="C40" t="n">
         <v>16.02000045776367</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>5.519486904144287</v>
+        <v>5.519485950469971</v>
       </c>
       <c r="C41" t="n">
         <v>16.32999992370605</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>5.776363849639893</v>
+        <v>5.776365756988525</v>
       </c>
       <c r="C42" t="n">
         <v>17.09000015258789</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>6.03827953338623</v>
+        <v>6.038278579711914</v>
       </c>
       <c r="C44" t="n">
         <v>17.53000068664551</v>
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>6.249392986297607</v>
+        <v>6.249395847320557</v>
       </c>
       <c r="C46" t="n">
         <v>17.80999946594238</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>6.35466194152832</v>
+        <v>6.354662418365479</v>
       </c>
       <c r="C47" t="n">
         <v>18.11000061035156</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>6.60028600692749</v>
+        <v>6.600286960601807</v>
       </c>
       <c r="C48" t="n">
         <v>18.80999946594238</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>7.004937648773193</v>
+        <v>7.004939556121826</v>
       </c>
       <c r="C49" t="n">
         <v>19.6299991607666</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>7.087017059326172</v>
+        <v>7.087016582489014</v>
       </c>
       <c r="C50" t="n">
         <v>19.86000061035156</v>
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>7.44773530960083</v>
+        <v>7.44774055480957</v>
       </c>
       <c r="C52" t="n">
         <v>20.52000045776367</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>7.690913200378418</v>
+        <v>7.690910816192627</v>
       </c>
       <c r="C53" t="n">
         <v>21.19000053405762</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>7.364260673522949</v>
+        <v>7.364257335662842</v>
       </c>
       <c r="C54" t="n">
         <v>20.29000091552734</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>7.400996685028076</v>
+        <v>7.400997638702393</v>
       </c>
       <c r="C55" t="n">
         <v>20.04000091552734</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>8.183938026428223</v>
+        <v>8.183937072753906</v>
       </c>
       <c r="C56" t="n">
         <v>22.15999984741211</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>8.24302864074707</v>
+        <v>8.243029594421387</v>
       </c>
       <c r="C57" t="n">
         <v>22.31999969482422</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>9.014545440673828</v>
+        <v>9.014544486999512</v>
       </c>
       <c r="C58" t="n">
         <v>24.02000045776367</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>9.539955139160156</v>
+        <v>9.539958000183105</v>
       </c>
       <c r="C59" t="n">
         <v>25.42000007629395</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>9.007040977478027</v>
+        <v>9.007039070129395</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>9.380845069885254</v>
+        <v>9.380840301513672</v>
       </c>
       <c r="C61" t="n">
         <v>24.6200008392334</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>8.957904815673828</v>
+        <v>8.957901954650879</v>
       </c>
       <c r="C62" t="n">
         <v>23.51000022888184</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>9.666607856750488</v>
+        <v>9.666613578796387</v>
       </c>
       <c r="C63" t="n">
         <v>25.3700008392334</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>10.06729125976562</v>
+        <v>10.06729316711426</v>
       </c>
       <c r="C64" t="n">
         <v>26.03000068664551</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>10.38056659698486</v>
+        <v>10.38056373596191</v>
       </c>
       <c r="C65" t="n">
         <v>26.84000015258789</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.85240936279297</v>
+        <v>10.85240840911865</v>
       </c>
       <c r="C66" t="n">
         <v>28.05999946594238</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>10.36001300811768</v>
+        <v>10.36001586914062</v>
       </c>
       <c r="C67" t="n">
         <v>26.40999984741211</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>10.31685733795166</v>
+        <v>10.31686115264893</v>
       </c>
       <c r="C68" t="n">
         <v>26.29999923706055</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>10.66598606109619</v>
+        <v>10.66599273681641</v>
       </c>
       <c r="C69" t="n">
         <v>27.19000053405762</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>10.68194007873535</v>
+        <v>10.68194389343262</v>
       </c>
       <c r="C70" t="n">
         <v>26.80999946594238</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>10.97678279876709</v>
+        <v>10.97677898406982</v>
       </c>
       <c r="C71" t="n">
         <v>27.54999923706055</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>11.43099117279053</v>
+        <v>11.43098926544189</v>
       </c>
       <c r="C72" t="n">
         <v>28.69000053405762</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>11.97547626495361</v>
+        <v>11.97547721862793</v>
       </c>
       <c r="C73" t="n">
         <v>29.64999961853027</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>11.47060680389404</v>
+        <v>11.47060585021973</v>
       </c>
       <c r="C74" t="n">
         <v>28.39999961853027</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>12.15723037719727</v>
+        <v>12.15722942352295</v>
       </c>
       <c r="C75" t="n">
         <v>30.10000038146973</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>12.63846015930176</v>
+        <v>12.63845825195312</v>
       </c>
       <c r="C76" t="n">
         <v>30.8700008392334</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>13.18706321716309</v>
+        <v>13.18706703186035</v>
       </c>
       <c r="C77" t="n">
         <v>32.20999908447266</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>13.17887878417969</v>
+        <v>13.17887592315674</v>
       </c>
       <c r="C78" t="n">
         <v>32.18999862670898</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>14.32071876525879</v>
+        <v>14.32072067260742</v>
       </c>
       <c r="C79" t="n">
         <v>34.54999923706055</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>14.90929889678955</v>
+        <v>14.90929985046387</v>
       </c>
       <c r="C80" t="n">
         <v>35.97000122070312</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>14.07616519927979</v>
+        <v>14.07616996765137</v>
       </c>
       <c r="C81" t="n">
         <v>33.95999908447266</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>14.0192756652832</v>
+        <v>14.01927375793457</v>
       </c>
       <c r="C82" t="n">
         <v>33.38999938964844</v>
@@ -2329,7 +2341,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>14.19561672210693</v>
+        <v>14.19562244415283</v>
       </c>
       <c r="C84" t="n">
         <v>33.81000137329102</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>13.38080978393555</v>
+        <v>13.38080883026123</v>
       </c>
       <c r="C85" t="n">
         <v>31.44000053405762</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>14.33414649963379</v>
+        <v>14.33414745330811</v>
       </c>
       <c r="C86" t="n">
         <v>33.68000030517578</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>14.27882099151611</v>
+        <v>14.27881717681885</v>
       </c>
       <c r="C87" t="n">
         <v>33.54999923706055</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>14.82730674743652</v>
+        <v>14.82730484008789</v>
       </c>
       <c r="C88" t="n">
         <v>34.38999938964844</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>15.74135112762451</v>
+        <v>15.7413501739502</v>
       </c>
       <c r="C89" t="n">
         <v>36.5099983215332</v>
@@ -2532,7 +2544,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2561,7 +2573,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>15.30237865447998</v>
+        <v>15.30238056182861</v>
       </c>
       <c r="C92" t="n">
         <v>35.06000137329102</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>14.787353515625</v>
+        <v>14.78735542297363</v>
       </c>
       <c r="C93" t="n">
         <v>33.88000106811523</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>15.19851207733154</v>
+        <v>15.19851398468018</v>
       </c>
       <c r="C94" t="n">
         <v>34.34999847412109</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>16.47280120849609</v>
+        <v>16.47280311584473</v>
       </c>
       <c r="C95" t="n">
         <v>37.22999954223633</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>16.36218643188477</v>
+        <v>16.36218070983887</v>
       </c>
       <c r="C96" t="n">
         <v>36.97999954223633</v>
@@ -2735,7 +2747,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>15.77983379364014</v>
+        <v>15.7798376083374</v>
       </c>
       <c r="C98" t="n">
         <v>35.22000122070312</v>
@@ -2793,7 +2805,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>16.99186897277832</v>
+        <v>16.99187278747559</v>
       </c>
       <c r="C100" t="n">
         <v>37.43000030517578</v>
@@ -2851,7 +2863,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>18.86673927307129</v>
+        <v>18.86674499511719</v>
       </c>
       <c r="C102" t="n">
         <v>41.56000137329102</v>
@@ -2909,7 +2921,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>18.64101791381836</v>
+        <v>18.64102363586426</v>
       </c>
       <c r="C104" t="n">
         <v>40.59999847412109</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>19.77968215942383</v>
+        <v>19.77968978881836</v>
       </c>
       <c r="C105" t="n">
         <v>43.08000183105469</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>21.34589195251465</v>
+        <v>21.34589576721191</v>
       </c>
       <c r="C106" t="n">
         <v>45.93999862670898</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>22.4610481262207</v>
+        <v>22.46104621887207</v>
       </c>
       <c r="C107" t="n">
         <v>48.34000015258789</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>23.35316848754883</v>
+        <v>23.35317230224609</v>
       </c>
       <c r="C108" t="n">
         <v>50.2599983215332</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>23.13106536865234</v>
+        <v>23.13106155395508</v>
       </c>
       <c r="C109" t="n">
         <v>49.27000045776367</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>24.92916107177734</v>
+        <v>24.92916870117188</v>
       </c>
       <c r="C110" t="n">
         <v>53.09999847412109</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>26.42678451538086</v>
+        <v>26.42679023742676</v>
       </c>
       <c r="C111" t="n">
         <v>56.29000091552734</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>23.71937370300293</v>
+        <v>23.7193717956543</v>
       </c>
       <c r="C112" t="n">
         <v>50.02000045776367</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>23.73359489440918</v>
+        <v>23.73359107971191</v>
       </c>
       <c r="C113" t="n">
         <v>50.04999923706055</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>24.27892303466797</v>
+        <v>24.27892684936523</v>
       </c>
       <c r="C114" t="n">
         <v>51.20000076293945</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>23.44065856933594</v>
+        <v>23.44066047668457</v>
       </c>
       <c r="C115" t="n">
         <v>48.90999984741211</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>26.06220626831055</v>
+        <v>26.06221389770508</v>
       </c>
       <c r="C116" t="n">
         <v>54.38000106811523</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>25.67880439758301</v>
+        <v>25.67881011962891</v>
       </c>
       <c r="C117" t="n">
         <v>53.58000183105469</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>26.35128784179688</v>
+        <v>26.35129356384277</v>
       </c>
       <c r="C118" t="n">
         <v>54.40000152587891</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>29.29159545898438</v>
+        <v>29.29159736633301</v>
       </c>
       <c r="C119" t="n">
         <v>60.47000122070312</v>
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>27.90136337280273</v>
+        <v>27.9013614654541</v>
       </c>
       <c r="C120" t="n">
         <v>57.59999847412109</v>
@@ -3431,7 +3443,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>29.89567375183105</v>
+        <v>29.89566802978516</v>
       </c>
       <c r="C122" t="n">
         <v>61.11000061035156</v>
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>30.12070846557617</v>
+        <v>30.12070655822754</v>
       </c>
       <c r="C123" t="n">
         <v>61.56999969482422</v>
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>30.93133926391602</v>
+        <v>30.93134689331055</v>
       </c>
       <c r="C124" t="n">
         <v>62.65999984741211</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>30.95602798461914</v>
+        <v>30.95602607727051</v>
       </c>
       <c r="C125" t="n">
         <v>62.70999908447266</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>31.41510581970215</v>
+        <v>31.41511726379395</v>
       </c>
       <c r="C126" t="n">
         <v>63.63999938964844</v>
@@ -3605,7 +3617,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>33.70727157592773</v>
+        <v>33.70727920532227</v>
       </c>
       <c r="C128" t="n">
         <v>67.69999694824219</v>
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>32.90567016601562</v>
+        <v>32.90566253662109</v>
       </c>
       <c r="C129" t="n">
         <v>66.08999633789062</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>31.78146362304688</v>
+        <v>31.78147315979004</v>
       </c>
       <c r="C130" t="n">
         <v>63.22999954223633</v>
@@ -3721,7 +3733,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3750,7 +3762,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>34.29677200317383</v>
+        <v>34.29679107666016</v>
       </c>
       <c r="C133" t="n">
         <v>67.62000274658203</v>
@@ -3808,11 +3820,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>36.10240936279297</v>
+        <v>36.1024169921875</v>
       </c>
       <c r="C134" t="n">
         <v>71.18000030517578</v>
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>37.99932098388672</v>
+        <v>37.99934005737305</v>
       </c>
       <c r="C135" t="n">
         <v>74.91999816894531</v>
@@ -3866,11 +3878,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>36.51548767089844</v>
+        <v>36.51549911499023</v>
       </c>
       <c r="C136" t="n">
         <v>71.41999816894531</v>
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>36.69956970214844</v>
+        <v>36.69955444335938</v>
       </c>
       <c r="C137" t="n">
         <v>71.77999877929688</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>38.57082748413086</v>
+        <v>38.57083892822266</v>
       </c>
       <c r="C138" t="n">
         <v>75.44000244140625</v>
@@ -3953,7 +3965,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3982,11 +3994,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>33.48867797851562</v>
+        <v>33.48868179321289</v>
       </c>
       <c r="C140" t="n">
         <v>64.97000122070312</v>
@@ -4011,7 +4023,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>33.03857421875</v>
+        <v>33.03856658935547</v>
       </c>
       <c r="C142" t="n">
         <v>63.41999816894531</v>
@@ -4069,11 +4081,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>33.45532989501953</v>
+        <v>33.45531845092773</v>
       </c>
       <c r="C143" t="n">
         <v>64.22000122070312</v>
@@ -4098,11 +4110,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>35.3359489440918</v>
+        <v>35.33595657348633</v>
       </c>
       <c r="C144" t="n">
         <v>67.83000183105469</v>
@@ -4127,11 +4139,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>37.53619766235352</v>
+        <v>37.53618240356445</v>
       </c>
       <c r="C145" t="n">
         <v>71.41000366210938</v>
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>36.9737548828125</v>
+        <v>36.97374725341797</v>
       </c>
       <c r="C146" t="n">
         <v>70.33999633789062</v>
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>33.08923721313477</v>
+        <v>33.08925247192383</v>
       </c>
       <c r="C147" t="n">
         <v>62.95000076293945</v>
@@ -4214,7 +4226,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>29.80938148498535</v>
+        <v>29.80937576293945</v>
       </c>
       <c r="C149" t="n">
         <v>56.11000061035156</v>
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>29.6128101348877</v>
+        <v>29.61281967163086</v>
       </c>
       <c r="C150" t="n">
         <v>55.7400016784668</v>
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>30.54292106628418</v>
+        <v>30.54291725158691</v>
       </c>
       <c r="C151" t="n">
         <v>56.79000091552734</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>31.55941009521484</v>
+        <v>31.55941390991211</v>
       </c>
       <c r="C152" t="n">
         <v>58.68000030517578</v>
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>31.47335243225098</v>
+        <v>31.47335815429688</v>
       </c>
       <c r="C153" t="n">
         <v>58.52000045776367</v>
@@ -4388,7 +4400,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4417,7 +4429,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4442,11 +4454,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>29.86546897888184</v>
+        <v>29.8654727935791</v>
       </c>
       <c r="C156" t="n">
         <v>54.83000183105469</v>
@@ -4467,7 +4479,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4492,11 +4504,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>27.32586860656738</v>
+        <v>27.32587051391602</v>
       </c>
       <c r="C158" t="n">
         <v>49.34999847412109</v>
@@ -4517,11 +4529,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>29.0202465057373</v>
+        <v>29.02024078369141</v>
       </c>
       <c r="C159" t="n">
         <v>52.40999984741211</v>
@@ -4546,11 +4558,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>32.25312805175781</v>
+        <v>32.25312042236328</v>
       </c>
       <c r="C160" t="n">
         <v>57.43000030517578</v>
@@ -4575,11 +4587,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>30.51214790344238</v>
+        <v>30.51214218139648</v>
       </c>
       <c r="C161" t="n">
         <v>54.33000183105469</v>
@@ -4604,11 +4616,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>27.55246734619141</v>
+        <v>27.5524730682373</v>
       </c>
       <c r="C162" t="n">
         <v>49.06000137329102</v>
@@ -4633,7 +4645,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4662,11 +4674,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>26.85124969482422</v>
+        <v>26.85124206542969</v>
       </c>
       <c r="C164" t="n">
         <v>47.06999969482422</v>
@@ -4691,11 +4703,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>24.95164108276367</v>
+        <v>24.95163917541504</v>
       </c>
       <c r="C165" t="n">
         <v>43.7400016784668</v>
@@ -4720,11 +4732,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>23.78085517883301</v>
+        <v>23.78084945678711</v>
       </c>
       <c r="C166" t="n">
         <v>40.90000152587891</v>
@@ -4749,11 +4761,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>26.04264450073242</v>
+        <v>26.04265403747559</v>
       </c>
       <c r="C167" t="n">
         <v>44.79000091552734</v>
@@ -4774,11 +4786,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>28.89751625061035</v>
+        <v>28.89751815795898</v>
       </c>
       <c r="C168" t="n">
         <v>49.70000076293945</v>
@@ -4799,11 +4811,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>29.50032234191895</v>
+        <v>29.50032424926758</v>
       </c>
       <c r="C169" t="n">
         <v>49.90999984741211</v>
@@ -4824,11 +4836,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>28.09357261657715</v>
+        <v>28.09357070922852</v>
       </c>
       <c r="C170" t="n">
         <v>47.52999877929688</v>
@@ -4849,7 +4861,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4876,11 +4888,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>23.48535537719727</v>
+        <v>23.4853572845459</v>
       </c>
       <c r="C172" t="n">
         <v>38.66999816894531</v>
@@ -4903,11 +4915,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>23.83760452270508</v>
+        <v>23.83761024475098</v>
       </c>
       <c r="C173" t="n">
         <v>39.25</v>
@@ -4930,11 +4942,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>23.71614837646484</v>
+        <v>23.71614456176758</v>
       </c>
       <c r="C174" t="n">
         <v>39.04999923706055</v>
@@ -4957,11 +4969,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>24.35837364196777</v>
+        <v>24.35837745666504</v>
       </c>
       <c r="C175" t="n">
         <v>39.25</v>
@@ -4984,11 +4996,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>25.53751754760742</v>
+        <v>25.53751373291016</v>
       </c>
       <c r="C176" t="n">
         <v>41.15000152587891</v>
@@ -5011,11 +5023,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>27.14485359191895</v>
+        <v>27.14485740661621</v>
       </c>
       <c r="C177" t="n">
         <v>43.7400016784668</v>
@@ -5038,11 +5050,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>24.46244239807129</v>
+        <v>24.46244430541992</v>
       </c>
       <c r="C178" t="n">
         <v>38.63999938964844</v>
@@ -5065,11 +5077,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>22.84174537658691</v>
+        <v>22.84173965454102</v>
       </c>
       <c r="C179" t="n">
         <v>36.08000183105469</v>
@@ -5090,11 +5102,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>25.21581649780273</v>
+        <v>25.21581268310547</v>
       </c>
       <c r="C180" t="n">
         <v>39.83000183105469</v>
@@ -5115,11 +5127,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>26.48789596557617</v>
+        <v>26.48789215087891</v>
       </c>
       <c r="C181" t="n">
         <v>41</v>
@@ -5140,11 +5152,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>26.53957366943359</v>
+        <v>26.53957748413086</v>
       </c>
       <c r="C182" t="n">
         <v>41.08000183105469</v>
@@ -5165,11 +5177,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>28.16761207580566</v>
+        <v>28.16761016845703</v>
       </c>
       <c r="C183" t="n">
         <v>43.59999847412109</v>
@@ -5190,11 +5202,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>33.62420654296875</v>
+        <v>33.62422180175781</v>
       </c>
       <c r="C184" t="n">
         <v>51.15999984741211</v>
@@ -5215,11 +5227,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>31.38304901123047</v>
+        <v>31.38303756713867</v>
       </c>
       <c r="C185" t="n">
         <v>47.75</v>
@@ -5244,11 +5256,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>32.34917449951172</v>
+        <v>32.34917068481445</v>
       </c>
       <c r="C186" t="n">
         <v>49.22000122070312</v>
@@ -5273,7 +5285,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5302,11 +5314,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>32.12892150878906</v>
+        <v>32.12892532348633</v>
       </c>
       <c r="C188" t="n">
         <v>48.04000091552734</v>
@@ -5331,11 +5343,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>33.59357833862305</v>
+        <v>33.59358215332031</v>
       </c>
       <c r="C189" t="n">
         <v>50.22999954223633</v>
@@ -5360,11 +5372,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>31.00068283081055</v>
+        <v>31.00067520141602</v>
       </c>
       <c r="C190" t="n">
         <v>45.52000045776367</v>
@@ -5389,11 +5401,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>30.0404109954834</v>
+        <v>30.04041862487793</v>
       </c>
       <c r="C191" t="n">
         <v>44.11000061035156</v>
@@ -5418,11 +5430,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>29.03929138183594</v>
+        <v>29.03929710388184</v>
       </c>
       <c r="C192" t="n">
         <v>42.63999938964844</v>
@@ -5447,11 +5459,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>32.89393997192383</v>
+        <v>32.89394378662109</v>
       </c>
       <c r="C193" t="n">
         <v>47.38999938964844</v>
@@ -5476,11 +5488,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>35.3163948059082</v>
+        <v>35.31639099121094</v>
       </c>
       <c r="C194" t="n">
         <v>50.88000106811523</v>
@@ -5505,11 +5517,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>35.60098266601562</v>
+        <v>35.60097122192383</v>
       </c>
       <c r="C195" t="n">
         <v>51.29000091552734</v>
@@ -5534,7 +5546,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5563,7 +5575,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5592,7 +5604,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5621,7 +5633,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5650,11 +5662,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>31.56989479064941</v>
+        <v>31.56990242004395</v>
       </c>
       <c r="C200" t="n">
         <v>43.86000061035156</v>
@@ -5679,11 +5691,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>32.47683334350586</v>
+        <v>32.47682189941406</v>
       </c>
       <c r="C201" t="n">
         <v>45.11999893188477</v>
@@ -5708,11 +5720,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>29.71507263183594</v>
+        <v>29.71507453918457</v>
       </c>
       <c r="C202" t="n">
         <v>40.38000106811523</v>
@@ -5737,11 +5749,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>34.0494384765625</v>
+        <v>34.04944610595703</v>
       </c>
       <c r="C203" t="n">
         <v>46.27000045776367</v>
@@ -5766,11 +5778,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>34.27756881713867</v>
+        <v>34.27756500244141</v>
       </c>
       <c r="C204" t="n">
         <v>46.58000183105469</v>
@@ -5795,11 +5807,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>34.33226013183594</v>
+        <v>34.33226776123047</v>
       </c>
       <c r="C205" t="n">
         <v>45.70999908447266</v>
@@ -5824,11 +5836,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>33.82904052734375</v>
+        <v>33.82904434204102</v>
       </c>
       <c r="C206" t="n">
         <v>45.04000091552734</v>
@@ -5853,7 +5865,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5882,11 +5894,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>34.22615432739258</v>
+        <v>34.22615814208984</v>
       </c>
       <c r="C208" t="n">
         <v>44.61999893188477</v>
@@ -5911,11 +5923,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>36.44295120239258</v>
+        <v>36.44294357299805</v>
       </c>
       <c r="C209" t="n">
         <v>47.5099983215332</v>
@@ -5940,11 +5952,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>34.07273483276367</v>
+        <v>34.07273864746094</v>
       </c>
       <c r="C210" t="n">
         <v>44.41999816894531</v>
@@ -5969,11 +5981,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>35.47650909423828</v>
+        <v>35.47650527954102</v>
       </c>
       <c r="C211" t="n">
         <v>45.29999923706055</v>
@@ -5998,7 +6010,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6027,7 +6039,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6056,11 +6068,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>33.66860961914062</v>
+        <v>33.66861343383789</v>
       </c>
       <c r="C214" t="n">
         <v>42.04999923706055</v>
@@ -6085,11 +6097,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>32.16333389282227</v>
+        <v>32.16332244873047</v>
       </c>
       <c r="C215" t="n">
         <v>40.16999816894531</v>
@@ -6114,7 +6126,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6143,7 +6155,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6172,7 +6184,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6201,11 +6213,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>33.53009033203125</v>
+        <v>33.53008651733398</v>
       </c>
       <c r="C219" t="n">
         <v>40.90999984741211</v>
@@ -6230,7 +6242,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6259,11 +6271,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>36.70723724365234</v>
+        <v>36.70724105834961</v>
       </c>
       <c r="C221" t="n">
         <v>43.81000137329102</v>
@@ -6288,11 +6300,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>38.75165176391602</v>
+        <v>38.75165557861328</v>
       </c>
       <c r="C222" t="n">
         <v>46.25</v>
@@ -6317,11 +6329,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>39.00056076049805</v>
+        <v>39.00056838989258</v>
       </c>
       <c r="C223" t="n">
         <v>45.54999923706055</v>
@@ -6346,11 +6358,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>41.96306991577148</v>
+        <v>41.96305847167969</v>
       </c>
       <c r="C224" t="n">
         <v>49.0099983215332</v>
@@ -6375,7 +6387,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6404,7 +6416,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6433,11 +6445,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>47.54514694213867</v>
+        <v>47.54514312744141</v>
       </c>
       <c r="C227" t="n">
         <v>54.45999908447266</v>
@@ -6462,7 +6474,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6491,11 +6503,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>46.53844833374023</v>
+        <v>46.53844451904297</v>
       </c>
       <c r="C229" t="n">
         <v>52.29000091552734</v>
@@ -6520,7 +6532,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6549,7 +6561,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6578,11 +6590,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>54.38034057617188</v>
+        <v>54.38034820556641</v>
       </c>
       <c r="C232" t="n">
         <v>60.02000045776367</v>
@@ -6607,11 +6619,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>53.59209442138672</v>
+        <v>53.59209060668945</v>
       </c>
       <c r="C233" t="n">
         <v>59.15000152587891</v>
@@ -6636,11 +6648,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>54.91490936279297</v>
+        <v>54.9149055480957</v>
       </c>
       <c r="C234" t="n">
         <v>60.61000061035156</v>
@@ -6665,7 +6677,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6694,7 +6706,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6723,11 +6735,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>61.95127105712891</v>
+        <v>61.95126724243164</v>
       </c>
       <c r="C237" t="n">
         <v>67.20999908447266</v>
@@ -6752,11 +6764,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>61.87530517578125</v>
+        <v>61.87531280517578</v>
       </c>
       <c r="C238" t="n">
         <v>66.05999755859375</v>
@@ -6781,7 +6793,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6810,11 +6822,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>55.27190399169922</v>
+        <v>55.27190780639648</v>
       </c>
       <c r="C240" t="n">
         <v>59.0099983215332</v>
@@ -6839,7 +6851,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6868,7 +6880,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6897,7 +6909,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6926,7 +6938,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6955,7 +6967,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6984,11 +6996,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>67.47708892822266</v>
+        <v>67.47708129882812</v>
       </c>
       <c r="C246" t="n">
         <v>69.58000183105469</v>
@@ -7013,7 +7025,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7042,7 +7054,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7071,7 +7083,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7100,32 +7112,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>68.94999694824219</v>
+        <v>68.87999725341797</v>
       </c>
       <c r="C250" t="n">
-        <v>68.94999694824219</v>
+        <v>68.87999725341797</v>
       </c>
       <c r="D250" t="n">
-        <v>135524200</v>
+        <v>142904400</v>
       </c>
       <c r="E250" t="n">
         <v>4.75</v>
       </c>
       <c r="F250" t="n">
-        <v>14.51578883120888</v>
+        <v>14.50105205335115</v>
       </c>
       <c r="G250" t="n">
         <v>1669743926</v>
       </c>
       <c r="H250" t="n">
-        <v>115128838602.0459</v>
+        <v>115011957036.7913</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08116466117332054</v>
+        <v>0.08558462035693011</v>
       </c>
     </row>
   </sheetData>
@@ -7157,75 +7169,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7261,13 +7273,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7303,13 +7315,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7345,13 +7357,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7387,13 +7399,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7429,13 +7441,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7462,7 +7474,7 @@
       <c r="I7" t="n">
         <v>1.54</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7475,13 +7487,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7508,7 +7520,7 @@
       <c r="I8" t="n">
         <v>1.65</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7521,13 +7533,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7554,7 +7566,7 @@
       <c r="I9" t="n">
         <v>1.66</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7567,13 +7579,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7600,7 +7612,7 @@
       <c r="I10" t="n">
         <v>1.78</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7613,13 +7625,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7646,7 +7658,7 @@
       <c r="I11" t="n">
         <v>1.87</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7659,13 +7671,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7692,7 +7704,7 @@
       <c r="I12" t="n">
         <v>1.93</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="K12" t="n">
@@ -7705,13 +7717,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7738,7 +7750,7 @@
       <c r="I13" t="n">
         <v>1.64</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="K13" t="n">
@@ -7751,13 +7763,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7784,7 +7796,7 @@
       <c r="I14" t="n">
         <v>1.67</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="K14" t="n">
@@ -7797,13 +7809,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7830,7 +7842,7 @@
       <c r="I15" t="n">
         <v>1.64</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="K15" t="n">
@@ -7843,13 +7855,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7876,7 +7888,7 @@
       <c r="I16" t="n">
         <v>1.67</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="K16" t="n">
@@ -7889,13 +7901,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7922,7 +7934,7 @@
       <c r="I17" t="n">
         <v>2.06</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="K17" t="n">
@@ -7935,13 +7947,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7968,7 +7980,7 @@
       <c r="I18" t="n">
         <v>1.81</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="K18" t="n">
@@ -7981,13 +7993,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8014,7 +8026,7 @@
       <c r="I19" t="n">
         <v>1.95</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="K19" t="n">
@@ -8027,13 +8039,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8060,7 +8072,7 @@
       <c r="I20" t="n">
         <v>2.16</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="K20" t="n">
@@ -8073,13 +8085,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8106,7 +8118,7 @@
       <c r="I21" t="n">
         <v>2.19</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="K21" t="n">
@@ -8119,13 +8131,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8152,7 +8164,7 @@
       <c r="I22" t="n">
         <v>2.57</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="K22" t="n">
@@ -8165,13 +8177,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8198,7 +8210,7 @@
       <c r="I23" t="n">
         <v>2.26</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="K23" t="n">
@@ -8211,13 +8223,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8244,7 +8256,7 @@
       <c r="I24" t="n">
         <v>2.16</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="K24" t="n">
@@ -8257,13 +8269,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41842</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8290,7 +8302,7 @@
       <c r="I25" t="n">
         <v>2.17</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41842</v>
       </c>
       <c r="K25" t="n">
@@ -8303,13 +8315,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8336,7 +8348,7 @@
       <c r="I26" t="n">
         <v>2.18</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="K26" t="n">
@@ -8349,13 +8361,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8382,7 +8394,7 @@
       <c r="I27" t="n">
         <v>2.57</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="K27" t="n">
@@ -8395,13 +8407,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8428,7 +8440,7 @@
       <c r="I28" t="n">
         <v>2.5</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="K28" t="n">
@@ -8441,13 +8453,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8474,7 +8486,7 @@
       <c r="I29" t="n">
         <v>2.6</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="K29" t="n">
@@ -8487,13 +8499,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8520,7 +8532,7 @@
       <c r="I30" t="n">
         <v>2.67</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="K30" t="n">
@@ -8533,13 +8545,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8566,7 +8578,7 @@
       <c r="I31" t="n">
         <v>2.68</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K31" t="n">
@@ -8579,13 +8591,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8612,7 +8624,7 @@
       <c r="I32" t="n">
         <v>2.78</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="K32" t="n">
@@ -8625,13 +8637,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8658,7 +8670,7 @@
       <c r="I33" t="n">
         <v>2.88</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="K33" t="n">
@@ -8671,13 +8683,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8704,7 +8716,7 @@
       <c r="I34" t="n">
         <v>2.66</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="K34" t="n">
@@ -8717,13 +8729,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8750,7 +8762,7 @@
       <c r="I35" t="n">
         <v>7.289999999999999</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="K35" t="n">
@@ -8763,13 +8775,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8796,7 +8808,7 @@
       <c r="I36" t="n">
         <v>7.389999999999999</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="K36" t="n">
@@ -8809,13 +8821,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8842,7 +8854,7 @@
       <c r="I37" t="n">
         <v>7.579999999999999</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K37" t="n">
@@ -8855,13 +8867,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8888,7 +8900,7 @@
       <c r="I38" t="n">
         <v>7.989999999999999</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K38" t="n">
@@ -8901,13 +8913,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8934,7 +8946,7 @@
       <c r="I39" t="n">
         <v>5.32</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="K39" t="n">
@@ -8947,13 +8959,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8980,7 +8992,7 @@
       <c r="I40" t="n">
         <v>5.600000000000001</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="K40" t="n">
@@ -8993,13 +9005,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9026,7 +9038,7 @@
       <c r="I41" t="n">
         <v>5.56</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="K41" t="n">
@@ -9039,13 +9051,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9072,7 +9084,7 @@
       <c r="I42" t="n">
         <v>5.620000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="K42" t="n">
@@ -9085,13 +9097,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9118,7 +9130,7 @@
       <c r="I43" t="n">
         <v>3.68</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="K43" t="n">
@@ -9131,13 +9143,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9164,7 +9176,7 @@
       <c r="I44" t="n">
         <v>3.28</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="K44" t="n">
@@ -9177,13 +9189,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9210,7 +9222,7 @@
       <c r="I45" t="n">
         <v>3.36</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="K45" t="n">
@@ -9223,13 +9235,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9256,7 +9268,7 @@
       <c r="I46" t="n">
         <v>0.9400000000000002</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="K46" t="n">
@@ -9269,13 +9281,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9302,7 +9314,7 @@
       <c r="I47" t="n">
         <v>-0.7199999999999999</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="K47" t="n">
@@ -9315,13 +9327,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9348,7 +9360,7 @@
       <c r="I48" t="n">
         <v>-0.4899999999999999</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K48" t="n">
@@ -9361,13 +9373,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9394,7 +9406,7 @@
       <c r="I49" t="n">
         <v>-0.5148144163528778</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K49" t="n">
@@ -9407,13 +9419,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9440,7 +9452,7 @@
       <c r="I50" t="n">
         <v>0.3651855836471223</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K50" t="n">
@@ -9453,13 +9465,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9486,7 +9498,7 @@
       <c r="I51" t="n">
         <v>2.395185583647122</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K51" t="n">
@@ -9499,13 +9511,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9532,7 +9544,7 @@
       <c r="I52" t="n">
         <v>2.335185583647122</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K52" t="n">
@@ -9545,13 +9557,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9578,7 +9590,7 @@
       <c r="I53" t="n">
         <v>2.45</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K53" t="n">
@@ -9591,13 +9603,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9624,7 +9636,7 @@
       <c r="I54" t="n">
         <v>1.48</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K54" t="n">
@@ -9637,13 +9649,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9670,7 +9682,7 @@
       <c r="I55" t="n">
         <v>1.34</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="K55" t="n">
@@ -9683,13 +9695,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9716,7 +9728,7 @@
       <c r="I56" t="n">
         <v>1.65</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K56" t="n">
@@ -9729,13 +9741,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9762,7 +9774,7 @@
       <c r="I57" t="n">
         <v>0.9800000000000002</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K57" t="n">
@@ -9775,13 +9787,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9808,7 +9820,7 @@
       <c r="I58" t="n">
         <v>2.58</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K58" t="n">
@@ -9821,13 +9833,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9854,7 +9866,7 @@
       <c r="I59" t="n">
         <v>3.19</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="K59" t="n">
@@ -9867,13 +9879,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9900,7 +9912,7 @@
       <c r="I60" t="n">
         <v>3.11</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K60" t="n">
@@ -9913,13 +9925,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9946,7 +9958,7 @@
       <c r="I61" t="n">
         <v>3.81</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="K61" t="n">
@@ -9959,13 +9971,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9992,7 +10004,7 @@
       <c r="I62" t="n">
         <v>4.91</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="K62" t="n">
@@ -10005,13 +10017,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10038,7 +10050,7 @@
       <c r="I63" t="n">
         <v>4.57</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="K63" t="n">
@@ -10051,13 +10063,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10084,7 +10096,7 @@
       <c r="I64" t="n">
         <v>4.78</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="K64" t="n">
@@ -10097,13 +10109,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10130,7 +10142,7 @@
       <c r="I65" t="n">
         <v>5.800000000000001</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="K65" t="n">
@@ -10143,13 +10155,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10176,7 +10188,7 @@
       <c r="I66" t="n">
         <v>5.920000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K66" t="n">
@@ -10189,13 +10201,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10222,7 +10234,7 @@
       <c r="I67" t="n">
         <v>6.540000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="K67" t="n">
@@ -10235,13 +10247,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10268,7 +10280,7 @@
       <c r="I68" t="n">
         <v>5.960000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="K68" t="n">
@@ -10281,13 +10293,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10314,7 +10326,7 @@
       <c r="I69" t="n">
         <v>5.16</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="K69" t="n">
@@ -10327,13 +10339,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10360,7 +10372,7 @@
       <c r="I70" t="n">
         <v>5.23</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K70" t="n">
@@ -10373,13 +10385,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10406,7 +10418,7 @@
       <c r="I71" t="n">
         <v>4.12</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="K71" t="n">
@@ -10419,13 +10431,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10452,7 +10464,7 @@
       <c r="I72" t="n">
         <v>4.79</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K72" t="n">
@@ -10465,13 +10477,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10498,7 +10510,7 @@
       <c r="I73" t="n">
         <v>4.75</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="K73" t="n">
@@ -10535,52 +10547,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40014</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="C2" t="n">
@@ -10609,10 +10621,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40106</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="C3" t="n">
@@ -10641,10 +10653,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40207</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40233</v>
       </c>
       <c r="C4" t="n">
@@ -10673,10 +10685,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40287</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="C5" t="n">
@@ -10705,10 +10717,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40379</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40416</v>
       </c>
       <c r="C6" t="n">
@@ -10737,10 +10749,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40471</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="C7" t="n">
@@ -10769,10 +10781,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10801,10 +10813,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40651</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="C9" t="n">
@@ -10833,10 +10845,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40742</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="C10" t="n">
@@ -10865,10 +10877,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40837</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="C11" t="n">
@@ -10897,10 +10909,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="C12" t="n">
@@ -10929,10 +10941,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41015</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="C13" t="n">
@@ -10961,10 +10973,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41106</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="C14" t="n">
@@ -10993,10 +11005,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41201</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="C15" t="n">
@@ -11025,10 +11037,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41320</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="C16" t="n">
@@ -11057,10 +11069,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41379</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="C17" t="n">
@@ -11089,10 +11101,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41470</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="C18" t="n">
@@ -11121,10 +11133,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41562</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="C19" t="n">
@@ -11153,10 +11165,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="C20" t="n">
@@ -11185,10 +11197,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41744</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="C21" t="n">
@@ -11217,10 +11229,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41834</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41842</v>
       </c>
       <c r="C22" t="n">
@@ -11249,10 +11261,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41932</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="C23" t="n">
@@ -11281,10 +11293,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42048</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="C24" t="n">
@@ -11313,10 +11325,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42108</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="C25" t="n">
@@ -11345,10 +11357,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42205</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="C26" t="n">
@@ -11377,10 +11389,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42296</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="C27" t="n">
@@ -11409,10 +11421,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42412</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C28" t="n">
@@ -11441,10 +11453,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42479</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="C29" t="n">
@@ -11473,10 +11485,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42569</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="C30" t="n">
@@ -11505,10 +11517,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42660</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="C31" t="n">
@@ -11537,10 +11549,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42779</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="C32" t="n">
@@ -11569,10 +11581,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42849</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="C33" t="n">
@@ -11601,10 +11613,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42934</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C34" t="n">
@@ -11633,10 +11645,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43024</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C35" t="n">
@@ -11665,10 +11677,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43144</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="C36" t="n">
@@ -11697,10 +11709,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43206</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C37" t="n">
@@ -11729,10 +11741,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43297</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C38" t="n">
@@ -11761,10 +11773,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43388</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="C39" t="n">
@@ -11793,10 +11805,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43508</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="C40" t="n">
@@ -11825,10 +11837,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43570</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="C41" t="n">
@@ -11857,10 +11869,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43668</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="C42" t="n">
@@ -11889,10 +11901,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43760</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C43" t="n">
@@ -11921,10 +11933,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43875</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="C44" t="n">
@@ -11953,10 +11965,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43942</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="C45" t="n">
@@ -11985,10 +11997,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44036</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="C46" t="n">
@@ -12017,10 +12029,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44125</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C47" t="n">
@@ -12049,10 +12061,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44242</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="C48" t="n">
@@ -12081,10 +12093,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44306</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C49" t="n">
@@ -12113,10 +12125,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44397</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C50" t="n">
@@ -12145,10 +12157,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44490</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C51" t="n">
@@ -12177,10 +12189,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44607</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="C52" t="n">
@@ -12209,10 +12221,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44670</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C53" t="n">
@@ -12241,10 +12253,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44761</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C54" t="n">
@@ -12273,10 +12285,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44852</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C55" t="n">
@@ -12305,10 +12317,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44972</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="C56" t="n">
@@ -12337,10 +12349,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45034</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C57" t="n">
@@ -12369,10 +12381,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="C58" t="n">
@@ -12401,10 +12413,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45216</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="C59" t="n">
@@ -12433,10 +12445,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45337</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45349</v>
       </c>
       <c r="C60" t="n">
@@ -12465,10 +12477,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45398</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="C61" t="n">
@@ -12497,10 +12509,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45497</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="C62" t="n">
@@ -12529,10 +12541,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45587</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C63" t="n">
@@ -12561,10 +12573,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45702</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="C64" t="n">
@@ -12593,10 +12605,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45768</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="C65" t="n">
@@ -12625,10 +12637,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45861</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="C66" t="n">
@@ -12657,10 +12669,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45952</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C67" t="n">
@@ -12689,10 +12701,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="C68" t="n">
@@ -12721,10 +12733,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C69" t="n">
@@ -12753,10 +12765,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46225</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="C70" t="n">
@@ -12803,12 +12815,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/MO.xlsx
+++ b/salidas/empresas/MO.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>4.802681446075439</v>
+        <v>4.802683353424072</v>
       </c>
       <c r="C2" t="n">
         <v>72.33999633789062</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>4.773470878601074</v>
+        <v>4.773470401763916</v>
       </c>
       <c r="C3" t="n">
         <v>71.90000152587891</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>4.755938529968262</v>
+        <v>4.755937099456787</v>
       </c>
       <c r="C4" t="n">
         <v>70.86000061035156</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>4.910307884216309</v>
+        <v>4.910309791564941</v>
       </c>
       <c r="C5" t="n">
         <v>73.16000366210938</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>4.855941772460938</v>
+        <v>4.855942726135254</v>
       </c>
       <c r="C6" t="n">
         <v>72.34999847412109</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>5.428467273712158</v>
+        <v>5.428465843200684</v>
       </c>
       <c r="C8" t="n">
         <v>79.97000122070312</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>5.670121192932129</v>
+        <v>5.670122146606445</v>
       </c>
       <c r="C9" t="n">
         <v>83.52999877929688</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>5.250678062438965</v>
+        <v>5.250676155090332</v>
       </c>
       <c r="C10" t="n">
         <v>76.55000305175781</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>5.57854175567627</v>
+        <v>5.578542709350586</v>
       </c>
       <c r="C11" t="n">
         <v>81.33000183105469</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>5.776089668273926</v>
+        <v>5.776086330413818</v>
       </c>
       <c r="C12" t="n">
         <v>84.20999908447266</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>5.946176052093506</v>
+        <v>5.946177005767822</v>
       </c>
       <c r="C13" t="n">
         <v>85.81999969482422</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>6.054953575134277</v>
+        <v>6.054956912994385</v>
       </c>
       <c r="C14" t="n">
         <v>87.38999938964844</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>5.839474678039551</v>
+        <v>5.839473724365234</v>
       </c>
       <c r="C15" t="n">
         <v>84.27999877929688</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>6.145037174224854</v>
+        <v>6.145036697387695</v>
       </c>
       <c r="C16" t="n">
         <v>87.80999755859375</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>6.629826068878174</v>
+        <v>6.629828929901123</v>
       </c>
       <c r="C18" t="n">
         <v>71.09999847412109</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>6.605288982391357</v>
+        <v>6.605289459228516</v>
       </c>
       <c r="C19" t="n">
         <v>70.13999938964844</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>6.259672164916992</v>
+        <v>6.259674072265625</v>
       </c>
       <c r="C20" t="n">
         <v>66.47000122070312</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>6.536543846130371</v>
+        <v>6.536541938781738</v>
       </c>
       <c r="C21" t="n">
         <v>69.41000366210938</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>6.621150016784668</v>
+        <v>6.621151924133301</v>
       </c>
       <c r="C22" t="n">
         <v>69.52999877929688</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>6.944925785064697</v>
+        <v>6.944925308227539</v>
       </c>
       <c r="C23" t="n">
         <v>72.93000030517578</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>7.385823249816895</v>
+        <v>7.38582706451416</v>
       </c>
       <c r="C24" t="n">
         <v>77.55999755859375</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>7.267497539520264</v>
+        <v>7.267499446868896</v>
       </c>
       <c r="C25" t="n">
         <v>75.58000183105469</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>7.032878398895264</v>
+        <v>7.032877445220947</v>
       </c>
       <c r="C27" t="n">
         <v>73.13999938964844</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>6.994595050811768</v>
+        <v>6.994594097137451</v>
       </c>
       <c r="C28" t="n">
         <v>22.20000076293945</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>6.301435947418213</v>
+        <v>6.301433563232422</v>
       </c>
       <c r="C29" t="n">
         <v>20</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>7.013497352600098</v>
+        <v>7.013495445251465</v>
       </c>
       <c r="C30" t="n">
         <v>22.26000022888184</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>6.568016529083252</v>
+        <v>6.568019866943359</v>
       </c>
       <c r="C31" t="n">
         <v>20.55999946594238</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>6.500932693481445</v>
+        <v>6.500933647155762</v>
       </c>
       <c r="C32" t="n">
         <v>20.35000038146973</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>6.718163013458252</v>
+        <v>6.718163967132568</v>
       </c>
       <c r="C33" t="n">
         <v>21.03000068664551</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>6.437233924865723</v>
+        <v>6.437234878540039</v>
       </c>
       <c r="C34" t="n">
         <v>19.84000015258789</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>6.226339817047119</v>
+        <v>6.226336002349854</v>
       </c>
       <c r="C35" t="n">
         <v>19.19000053405762</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>4.990850925445557</v>
+        <v>4.990847587585449</v>
       </c>
       <c r="C37" t="n">
         <v>15.0600004196167</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>5.481316089630127</v>
+        <v>5.481319904327393</v>
       </c>
       <c r="C38" t="n">
         <v>16.54000091552734</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>5.116780757904053</v>
+        <v>5.116779804229736</v>
       </c>
       <c r="C39" t="n">
         <v>15.4399995803833</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>5.519485950469971</v>
+        <v>5.519486904144287</v>
       </c>
       <c r="C41" t="n">
         <v>16.32999992370605</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>5.776365756988525</v>
+        <v>5.776365280151367</v>
       </c>
       <c r="C42" t="n">
         <v>17.09000015258789</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>5.645601749420166</v>
+        <v>5.645600318908691</v>
       </c>
       <c r="C43" t="n">
         <v>16.38999938964844</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>6.038278579711914</v>
+        <v>6.03827953338623</v>
       </c>
       <c r="C44" t="n">
         <v>17.53000068664551</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>6.29662036895752</v>
+        <v>6.296618461608887</v>
       </c>
       <c r="C45" t="n">
         <v>18.28000068664551</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>6.249395847320557</v>
+        <v>6.249392986297607</v>
       </c>
       <c r="C46" t="n">
         <v>17.80999946594238</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>6.354662418365479</v>
+        <v>6.354659557342529</v>
       </c>
       <c r="C47" t="n">
         <v>18.11000061035156</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>6.600286960601807</v>
+        <v>6.60028600692749</v>
       </c>
       <c r="C48" t="n">
         <v>18.80999946594238</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>7.004939556121826</v>
+        <v>7.004936218261719</v>
       </c>
       <c r="C49" t="n">
         <v>19.6299991607666</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>7.087016582489014</v>
+        <v>7.087014198303223</v>
       </c>
       <c r="C50" t="n">
         <v>19.86000061035156</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>7.179795742034912</v>
+        <v>7.179795265197754</v>
       </c>
       <c r="C51" t="n">
         <v>20.1200008392334</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>7.44774055480957</v>
+        <v>7.447737216949463</v>
       </c>
       <c r="C52" t="n">
         <v>20.52000045776367</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>7.690910816192627</v>
+        <v>7.690914154052734</v>
       </c>
       <c r="C53" t="n">
         <v>21.19000053405762</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>7.364257335662842</v>
+        <v>7.364259719848633</v>
       </c>
       <c r="C54" t="n">
         <v>20.29000091552734</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>7.400997638702393</v>
+        <v>7.400998592376709</v>
       </c>
       <c r="C55" t="n">
         <v>20.04000091552734</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>8.243029594421387</v>
+        <v>8.243026733398438</v>
       </c>
       <c r="C57" t="n">
         <v>22.31999969482422</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>9.014544486999512</v>
+        <v>9.014545440673828</v>
       </c>
       <c r="C58" t="n">
         <v>24.02000045776367</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>9.539958000183105</v>
+        <v>9.539958953857422</v>
       </c>
       <c r="C59" t="n">
         <v>25.42000007629395</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>9.007039070129395</v>
+        <v>9.007041931152344</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>9.380840301513672</v>
+        <v>9.380842208862305</v>
       </c>
       <c r="C61" t="n">
         <v>24.6200008392334</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>8.957901954650879</v>
+        <v>8.957904815673828</v>
       </c>
       <c r="C62" t="n">
         <v>23.51000022888184</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>9.666613578796387</v>
+        <v>9.666606903076172</v>
       </c>
       <c r="C63" t="n">
         <v>25.3700008392334</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>10.06729316711426</v>
+        <v>10.06729125976562</v>
       </c>
       <c r="C64" t="n">
         <v>26.03000068664551</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>10.38056373596191</v>
+        <v>10.38056468963623</v>
       </c>
       <c r="C65" t="n">
         <v>26.84000015258789</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.85240840911865</v>
+        <v>10.85241031646729</v>
       </c>
       <c r="C66" t="n">
         <v>28.05999946594238</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>10.36001586914062</v>
+        <v>10.36001300811768</v>
       </c>
       <c r="C67" t="n">
         <v>26.40999984741211</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>10.31686115264893</v>
+        <v>10.31686019897461</v>
       </c>
       <c r="C68" t="n">
         <v>26.29999923706055</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>10.66599273681641</v>
+        <v>10.66598606109619</v>
       </c>
       <c r="C69" t="n">
         <v>27.19000053405762</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>10.68194389343262</v>
+        <v>10.68194198608398</v>
       </c>
       <c r="C70" t="n">
         <v>26.80999946594238</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>10.97677898406982</v>
+        <v>10.97677993774414</v>
       </c>
       <c r="C71" t="n">
         <v>27.54999923706055</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>11.43098926544189</v>
+        <v>11.43099308013916</v>
       </c>
       <c r="C72" t="n">
         <v>28.69000053405762</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>11.97547721862793</v>
+        <v>11.9754753112793</v>
       </c>
       <c r="C73" t="n">
         <v>29.64999961853027</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>11.47060585021973</v>
+        <v>11.47060966491699</v>
       </c>
       <c r="C74" t="n">
         <v>28.39999961853027</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>12.15722942352295</v>
+        <v>12.15723133087158</v>
       </c>
       <c r="C75" t="n">
         <v>30.10000038146973</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>12.63845825195312</v>
+        <v>12.63845443725586</v>
       </c>
       <c r="C76" t="n">
         <v>30.8700008392334</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>13.18706703186035</v>
+        <v>13.18706321716309</v>
       </c>
       <c r="C77" t="n">
         <v>32.20999908447266</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>13.17887592315674</v>
+        <v>13.17887401580811</v>
       </c>
       <c r="C78" t="n">
         <v>32.18999862670898</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>14.32072067260742</v>
+        <v>14.32071876525879</v>
       </c>
       <c r="C79" t="n">
         <v>34.54999923706055</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>14.90929985046387</v>
+        <v>14.90929889678955</v>
       </c>
       <c r="C80" t="n">
         <v>35.97000122070312</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>13.35168838500977</v>
+        <v>13.35169315338135</v>
       </c>
       <c r="C83" t="n">
         <v>31.79999923706055</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>14.19562244415283</v>
+        <v>14.19562149047852</v>
       </c>
       <c r="C84" t="n">
         <v>33.81000137329102</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>13.38080883026123</v>
+        <v>13.38080310821533</v>
       </c>
       <c r="C85" t="n">
         <v>31.44000053405762</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>14.33414745330811</v>
+        <v>14.33414936065674</v>
       </c>
       <c r="C86" t="n">
         <v>33.68000030517578</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>14.27881717681885</v>
+        <v>14.27881908416748</v>
       </c>
       <c r="C87" t="n">
         <v>33.54999923706055</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>14.82730484008789</v>
+        <v>14.82730865478516</v>
       </c>
       <c r="C88" t="n">
         <v>34.38999938964844</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>15.7413501739502</v>
+        <v>15.74134635925293</v>
       </c>
       <c r="C89" t="n">
         <v>36.5099983215332</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>15.56457710266113</v>
+        <v>15.56457424163818</v>
       </c>
       <c r="C90" t="n">
         <v>36.09999847412109</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>15.27182579040527</v>
+        <v>15.27182674407959</v>
       </c>
       <c r="C91" t="n">
         <v>34.9900016784668</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>14.78735542297363</v>
+        <v>14.7873592376709</v>
       </c>
       <c r="C93" t="n">
         <v>33.88000106811523</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>16.47280311584473</v>
+        <v>16.47279930114746</v>
       </c>
       <c r="C95" t="n">
         <v>37.22999954223633</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>16.36218070983887</v>
+        <v>16.36218452453613</v>
       </c>
       <c r="C96" t="n">
         <v>36.97999954223633</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>15.7798376083374</v>
+        <v>15.77983570098877</v>
       </c>
       <c r="C98" t="n">
         <v>35.22000122070312</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>16.24579429626465</v>
+        <v>16.24579048156738</v>
       </c>
       <c r="C99" t="n">
         <v>36.2599983215332</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>16.99187278747559</v>
+        <v>16.99186515808105</v>
       </c>
       <c r="C100" t="n">
         <v>37.43000030517578</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>18.20849227905273</v>
+        <v>18.20849609375</v>
       </c>
       <c r="C101" t="n">
         <v>40.11000061035156</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>18.86674499511719</v>
+        <v>18.86673736572266</v>
       </c>
       <c r="C102" t="n">
         <v>41.56000137329102</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>19.25626945495605</v>
+        <v>19.25626182556152</v>
       </c>
       <c r="C103" t="n">
         <v>41.93999862670898</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>18.64102363586426</v>
+        <v>18.64102554321289</v>
       </c>
       <c r="C104" t="n">
         <v>40.59999847412109</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>19.77968978881836</v>
+        <v>19.77968788146973</v>
       </c>
       <c r="C105" t="n">
         <v>43.08000183105469</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>21.34589576721191</v>
+        <v>21.34589767456055</v>
       </c>
       <c r="C106" t="n">
         <v>45.93999862670898</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>22.46104621887207</v>
+        <v>22.46105194091797</v>
       </c>
       <c r="C107" t="n">
         <v>48.34000015258789</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>23.13106155395508</v>
+        <v>23.13107109069824</v>
       </c>
       <c r="C109" t="n">
         <v>49.27000045776367</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>24.92916870117188</v>
+        <v>24.92916107177734</v>
       </c>
       <c r="C110" t="n">
         <v>53.09999847412109</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>26.42679023742676</v>
+        <v>26.42679214477539</v>
       </c>
       <c r="C111" t="n">
         <v>56.29000091552734</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>23.73359107971191</v>
+        <v>23.73359489440918</v>
       </c>
       <c r="C113" t="n">
         <v>50.04999923706055</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>24.27892684936523</v>
+        <v>24.2789192199707</v>
       </c>
       <c r="C114" t="n">
         <v>51.20000076293945</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>23.44066047668457</v>
+        <v>23.4406566619873</v>
       </c>
       <c r="C115" t="n">
         <v>48.90999984741211</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>26.06221389770508</v>
+        <v>26.06221771240234</v>
       </c>
       <c r="C116" t="n">
         <v>54.38000106811523</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>25.67881011962891</v>
+        <v>25.67880821228027</v>
       </c>
       <c r="C117" t="n">
         <v>53.58000183105469</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>26.35129356384277</v>
+        <v>26.35128784179688</v>
       </c>
       <c r="C118" t="n">
         <v>54.40000152587891</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>29.29159736633301</v>
+        <v>29.29159355163574</v>
       </c>
       <c r="C119" t="n">
         <v>60.47000122070312</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>28.47695541381836</v>
+        <v>28.47696495056152</v>
       </c>
       <c r="C121" t="n">
         <v>58.20999908447266</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>29.89566802978516</v>
+        <v>29.89567565917969</v>
       </c>
       <c r="C122" t="n">
         <v>61.11000061035156</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>30.12070655822754</v>
+        <v>30.12070846557617</v>
       </c>
       <c r="C123" t="n">
         <v>61.56999969482422</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>30.93134689331055</v>
+        <v>30.93134880065918</v>
       </c>
       <c r="C124" t="n">
         <v>62.65999984741211</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>30.95602607727051</v>
+        <v>30.95602989196777</v>
       </c>
       <c r="C125" t="n">
         <v>62.70999908447266</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>31.41511726379395</v>
+        <v>31.41510963439941</v>
       </c>
       <c r="C126" t="n">
         <v>63.63999938964844</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>34.33460998535156</v>
+        <v>34.3346061706543</v>
       </c>
       <c r="C127" t="n">
         <v>68.95999908447266</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>33.70727920532227</v>
+        <v>33.70726776123047</v>
       </c>
       <c r="C128" t="n">
         <v>67.69999694824219</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>32.90566253662109</v>
+        <v>32.90565872192383</v>
       </c>
       <c r="C129" t="n">
         <v>66.08999633789062</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>31.78147315979004</v>
+        <v>31.78146934509277</v>
       </c>
       <c r="C130" t="n">
         <v>63.22999954223633</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>33.23408889770508</v>
+        <v>33.23408508300781</v>
       </c>
       <c r="C131" t="n">
         <v>66.12000274658203</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>34.29679107666016</v>
+        <v>34.29678344726562</v>
       </c>
       <c r="C133" t="n">
         <v>67.62000274658203</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>36.1024169921875</v>
+        <v>36.1024055480957</v>
       </c>
       <c r="C134" t="n">
         <v>71.18000030517578</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>37.99934005737305</v>
+        <v>37.99932861328125</v>
       </c>
       <c r="C135" t="n">
         <v>74.91999816894531</v>
@@ -3911,7 +3911,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>36.69955444335938</v>
+        <v>36.69956207275391</v>
       </c>
       <c r="C137" t="n">
         <v>71.77999877929688</v>
@@ -3969,7 +3969,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>38.38543701171875</v>
+        <v>38.38545227050781</v>
       </c>
       <c r="C139" t="n">
         <v>74.47000122070312</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>32.67942810058594</v>
+        <v>32.67943572998047</v>
       </c>
       <c r="C141" t="n">
         <v>63.40000152587891</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>33.03856658935547</v>
+        <v>33.03857803344727</v>
       </c>
       <c r="C142" t="n">
         <v>63.41999816894531</v>
@@ -4085,7 +4085,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>33.45531845092773</v>
+        <v>33.45532608032227</v>
       </c>
       <c r="C143" t="n">
         <v>64.22000122070312</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>35.33595657348633</v>
+        <v>35.33595275878906</v>
       </c>
       <c r="C144" t="n">
         <v>67.83000183105469</v>
@@ -4143,7 +4143,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>37.53618240356445</v>
+        <v>37.53618621826172</v>
       </c>
       <c r="C145" t="n">
         <v>71.41000366210938</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>36.97374725341797</v>
+        <v>36.9737434387207</v>
       </c>
       <c r="C146" t="n">
         <v>70.33999633789062</v>
@@ -4201,7 +4201,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>33.08925247192383</v>
+        <v>33.0892448425293</v>
       </c>
       <c r="C147" t="n">
         <v>62.95000076293945</v>
@@ -4259,7 +4259,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>29.80937576293945</v>
+        <v>29.80937385559082</v>
       </c>
       <c r="C149" t="n">
         <v>56.11000061035156</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>29.61281967163086</v>
+        <v>29.61282157897949</v>
       </c>
       <c r="C150" t="n">
         <v>55.7400016784668</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>30.54291725158691</v>
+        <v>30.54291915893555</v>
       </c>
       <c r="C151" t="n">
         <v>56.79000091552734</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>31.55941390991211</v>
+        <v>31.55940437316895</v>
       </c>
       <c r="C152" t="n">
         <v>58.68000030517578</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>31.47335815429688</v>
+        <v>31.47334861755371</v>
       </c>
       <c r="C153" t="n">
         <v>58.52000045776367</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>32.85037612915039</v>
+        <v>32.85037994384766</v>
       </c>
       <c r="C154" t="n">
         <v>60.31000137329102</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>35.42677307128906</v>
+        <v>35.42677688598633</v>
       </c>
       <c r="C155" t="n">
         <v>65.04000091552734</v>
@@ -4458,7 +4458,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>29.8654727935791</v>
+        <v>29.8654613494873</v>
       </c>
       <c r="C156" t="n">
         <v>54.83000183105469</v>
@@ -4533,7 +4533,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>29.02024078369141</v>
+        <v>29.02024269104004</v>
       </c>
       <c r="C159" t="n">
         <v>52.40999984741211</v>
@@ -4562,7 +4562,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>32.25312042236328</v>
+        <v>32.25312805175781</v>
       </c>
       <c r="C160" t="n">
         <v>57.43000030517578</v>
@@ -4591,7 +4591,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>30.51214218139648</v>
+        <v>30.51214408874512</v>
       </c>
       <c r="C161" t="n">
         <v>54.33000183105469</v>
@@ -4620,7 +4620,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>27.5524730682373</v>
+        <v>27.55247497558594</v>
       </c>
       <c r="C162" t="n">
         <v>49.06000137329102</v>
@@ -4649,7 +4649,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>27.0109748840332</v>
+        <v>27.01097869873047</v>
       </c>
       <c r="C163" t="n">
         <v>47.34999847412109</v>
@@ -4678,7 +4678,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>26.85124206542969</v>
+        <v>26.85124588012695</v>
       </c>
       <c r="C164" t="n">
         <v>47.06999969482422</v>
@@ -4707,7 +4707,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>24.95163917541504</v>
+        <v>24.95164489746094</v>
       </c>
       <c r="C165" t="n">
         <v>43.7400016784668</v>
@@ -4765,7 +4765,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>26.04265403747559</v>
+        <v>26.04264831542969</v>
       </c>
       <c r="C167" t="n">
         <v>44.79000091552734</v>
@@ -4790,7 +4790,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>28.89751815795898</v>
+        <v>28.89750862121582</v>
       </c>
       <c r="C168" t="n">
         <v>49.70000076293945</v>
@@ -4815,7 +4815,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>29.50032424926758</v>
+        <v>29.50031852722168</v>
       </c>
       <c r="C169" t="n">
         <v>49.90999984741211</v>
@@ -4840,7 +4840,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>28.09357070922852</v>
+        <v>28.09356689453125</v>
       </c>
       <c r="C170" t="n">
         <v>47.52999877929688</v>
@@ -4892,7 +4892,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>23.4853572845459</v>
+        <v>23.48536491394043</v>
       </c>
       <c r="C172" t="n">
         <v>38.66999816894531</v>
@@ -4919,7 +4919,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>23.83761024475098</v>
+        <v>23.83761215209961</v>
       </c>
       <c r="C173" t="n">
         <v>39.25</v>
@@ -4973,7 +4973,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>24.35837745666504</v>
+        <v>24.35837936401367</v>
       </c>
       <c r="C175" t="n">
         <v>39.25</v>
@@ -5000,7 +5000,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>25.53751373291016</v>
+        <v>25.53751182556152</v>
       </c>
       <c r="C176" t="n">
         <v>41.15000152587891</v>
@@ -5027,7 +5027,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>27.14485740661621</v>
+        <v>27.14486312866211</v>
       </c>
       <c r="C177" t="n">
         <v>43.7400016784668</v>
@@ -5054,7 +5054,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>24.46244430541992</v>
+        <v>24.46244621276855</v>
       </c>
       <c r="C178" t="n">
         <v>38.63999938964844</v>
@@ -5081,7 +5081,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>22.84173965454102</v>
+        <v>22.84173583984375</v>
       </c>
       <c r="C179" t="n">
         <v>36.08000183105469</v>
@@ -5106,7 +5106,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>25.21581268310547</v>
+        <v>25.2158203125</v>
       </c>
       <c r="C180" t="n">
         <v>39.83000183105469</v>
@@ -5131,7 +5131,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>26.48789215087891</v>
+        <v>26.48788833618164</v>
       </c>
       <c r="C181" t="n">
         <v>41</v>
@@ -5156,7 +5156,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>26.53957748413086</v>
+        <v>26.53957557678223</v>
       </c>
       <c r="C182" t="n">
         <v>41.08000183105469</v>
@@ -5181,7 +5181,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>28.16761016845703</v>
+        <v>28.16761207580566</v>
       </c>
       <c r="C183" t="n">
         <v>43.59999847412109</v>
@@ -5206,7 +5206,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>33.62422180175781</v>
+        <v>33.62421417236328</v>
       </c>
       <c r="C184" t="n">
         <v>51.15999984741211</v>
@@ -5260,7 +5260,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>32.34917068481445</v>
+        <v>32.34917831420898</v>
       </c>
       <c r="C186" t="n">
         <v>49.22000122070312</v>
@@ -5289,7 +5289,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>31.88815498352051</v>
+        <v>31.88815689086914</v>
       </c>
       <c r="C187" t="n">
         <v>47.68000030517578</v>
@@ -5347,7 +5347,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>33.59358215332031</v>
+        <v>33.59358596801758</v>
       </c>
       <c r="C189" t="n">
         <v>50.22999954223633</v>
@@ -5376,7 +5376,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>31.00067520141602</v>
+        <v>31.00067329406738</v>
       </c>
       <c r="C190" t="n">
         <v>45.52000045776367</v>
@@ -5405,7 +5405,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>30.04041862487793</v>
+        <v>30.04042053222656</v>
       </c>
       <c r="C191" t="n">
         <v>44.11000061035156</v>
@@ -5434,7 +5434,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>29.03929710388184</v>
+        <v>29.0392951965332</v>
       </c>
       <c r="C192" t="n">
         <v>42.63999938964844</v>
@@ -5463,7 +5463,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>32.89394378662109</v>
+        <v>32.89393997192383</v>
       </c>
       <c r="C193" t="n">
         <v>47.38999938964844</v>
@@ -5492,7 +5492,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>35.31639099121094</v>
+        <v>35.31638717651367</v>
       </c>
       <c r="C194" t="n">
         <v>50.88000106811523</v>
@@ -5521,7 +5521,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>35.60097122192383</v>
+        <v>35.60097503662109</v>
       </c>
       <c r="C195" t="n">
         <v>51.29000091552734</v>
@@ -5550,7 +5550,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>36.89118957519531</v>
+        <v>36.89118576049805</v>
       </c>
       <c r="C196" t="n">
         <v>52.25</v>
@@ -5579,7 +5579,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>39.23527908325195</v>
+        <v>39.23528289794922</v>
       </c>
       <c r="C197" t="n">
         <v>55.56999969482422</v>
@@ -5608,7 +5608,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>38.19032287597656</v>
+        <v>38.19032669067383</v>
       </c>
       <c r="C198" t="n">
         <v>54.09000015258789</v>
@@ -5637,7 +5637,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>30.0655345916748</v>
+        <v>30.06554222106934</v>
       </c>
       <c r="C199" t="n">
         <v>41.77000045776367</v>
@@ -5666,7 +5666,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>31.56990242004395</v>
+        <v>31.56989097595215</v>
       </c>
       <c r="C200" t="n">
         <v>43.86000061035156</v>
@@ -5695,7 +5695,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>32.47682189941406</v>
+        <v>32.47682571411133</v>
       </c>
       <c r="C201" t="n">
         <v>45.11999893188477</v>
@@ -5724,7 +5724,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>29.71507453918457</v>
+        <v>29.71506881713867</v>
       </c>
       <c r="C202" t="n">
         <v>40.38000106811523</v>
@@ -5753,7 +5753,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>34.04944610595703</v>
+        <v>34.04943466186523</v>
       </c>
       <c r="C203" t="n">
         <v>46.27000045776367</v>
@@ -5811,7 +5811,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>34.33226776123047</v>
+        <v>34.33226013183594</v>
       </c>
       <c r="C205" t="n">
         <v>45.70999908447266</v>
@@ -5840,7 +5840,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>33.82904434204102</v>
+        <v>33.82903289794922</v>
       </c>
       <c r="C206" t="n">
         <v>45.04000091552734</v>
@@ -5869,7 +5869,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>34.87305068969727</v>
+        <v>34.8730583190918</v>
       </c>
       <c r="C207" t="n">
         <v>46.43000030517578</v>
@@ -5898,7 +5898,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>34.22615814208984</v>
+        <v>34.22615432739258</v>
       </c>
       <c r="C208" t="n">
         <v>44.61999893188477</v>
@@ -5927,7 +5927,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>36.44294357299805</v>
+        <v>36.44294738769531</v>
       </c>
       <c r="C209" t="n">
         <v>47.5099983215332</v>
@@ -5956,7 +5956,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>34.07273864746094</v>
+        <v>34.07273483276367</v>
       </c>
       <c r="C210" t="n">
         <v>44.41999816894531</v>
@@ -5985,7 +5985,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>35.47650527954102</v>
+        <v>35.47650909423828</v>
       </c>
       <c r="C211" t="n">
         <v>45.29999923706055</v>
@@ -6072,7 +6072,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>33.66861343383789</v>
+        <v>33.66860580444336</v>
       </c>
       <c r="C214" t="n">
         <v>42.04999923706055</v>
@@ -6101,7 +6101,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>32.16332244873047</v>
+        <v>32.163330078125</v>
       </c>
       <c r="C215" t="n">
         <v>40.16999816894531</v>
@@ -6130,7 +6130,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>33.66060638427734</v>
+        <v>33.66060256958008</v>
       </c>
       <c r="C216" t="n">
         <v>42.04000091552734</v>
@@ -6159,7 +6159,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>33.06291198730469</v>
+        <v>33.06291961669922</v>
       </c>
       <c r="C217" t="n">
         <v>40.34000015258789</v>
@@ -6188,7 +6188,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>32.88260269165039</v>
+        <v>32.88259887695312</v>
       </c>
       <c r="C218" t="n">
         <v>40.11999893188477</v>
@@ -6217,7 +6217,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>33.53008651733398</v>
+        <v>33.53009033203125</v>
       </c>
       <c r="C219" t="n">
         <v>40.90999984741211</v>
@@ -6333,7 +6333,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>39.00056838989258</v>
+        <v>39.00056076049805</v>
       </c>
       <c r="C223" t="n">
         <v>45.54999923706055</v>
@@ -6362,7 +6362,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>41.96305847167969</v>
+        <v>41.96306991577148</v>
       </c>
       <c r="C224" t="n">
         <v>49.0099983215332</v>
@@ -6507,7 +6507,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>46.53844451904297</v>
+        <v>46.5384407043457</v>
       </c>
       <c r="C229" t="n">
         <v>52.29000091552734</v>
@@ -6536,7 +6536,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>46.48503875732422</v>
+        <v>46.48504638671875</v>
       </c>
       <c r="C230" t="n">
         <v>52.22999954223633</v>
@@ -6565,7 +6565,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>49.70686721801758</v>
+        <v>49.70686340332031</v>
       </c>
       <c r="C231" t="n">
         <v>55.84999847412109</v>
@@ -6594,7 +6594,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>54.38034820556641</v>
+        <v>54.38034439086914</v>
       </c>
       <c r="C232" t="n">
         <v>60.02000045776367</v>
@@ -6623,7 +6623,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>53.59209060668945</v>
+        <v>53.59209442138672</v>
       </c>
       <c r="C233" t="n">
         <v>59.15000152587891</v>
@@ -6652,7 +6652,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>54.9149055480957</v>
+        <v>54.91490173339844</v>
       </c>
       <c r="C234" t="n">
         <v>60.61000061035156</v>
@@ -6681,7 +6681,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>54.04259490966797</v>
+        <v>54.04259872436523</v>
       </c>
       <c r="C235" t="n">
         <v>58.63000106811523</v>
@@ -6710,7 +6710,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>57.09361267089844</v>
+        <v>57.09360885620117</v>
       </c>
       <c r="C236" t="n">
         <v>61.93999862670898</v>
@@ -6739,7 +6739,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>61.95126724243164</v>
+        <v>61.95127105712891</v>
       </c>
       <c r="C237" t="n">
         <v>67.20999908447266</v>
@@ -6768,7 +6768,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>61.87531280517578</v>
+        <v>61.87530517578125</v>
       </c>
       <c r="C238" t="n">
         <v>66.05999755859375</v>
@@ -6797,7 +6797,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>52.80850982666016</v>
+        <v>52.80851364135742</v>
       </c>
       <c r="C239" t="n">
         <v>56.38000106811523</v>
@@ -6826,7 +6826,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>55.27190780639648</v>
+        <v>55.27190399169922</v>
       </c>
       <c r="C240" t="n">
         <v>59.0099983215332</v>
@@ -6913,7 +6913,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>65.84999847412109</v>
+        <v>65.85000610351562</v>
       </c>
       <c r="C243" t="n">
         <v>69.04000091552734</v>
@@ -7000,7 +7000,7 @@
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>67.47708129882812</v>
+        <v>67.47708892822266</v>
       </c>
       <c r="C246" t="n">
         <v>69.58000183105469</v>
